--- a/evaluations/LLAMA3.2_Evaluation/Forkin-Finding-Questions.xlsx
+++ b/evaluations/LLAMA3.2_Evaluation/Forkin-Finding-Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Science UWA\Capstone\Capstone-Project-Evaluation\evaluations\LLAMA3.2_Evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590736A2-A4AE-47A5-A74C-31EE5012333F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{131EFB3E-22FF-4C00-817B-BE538DDDAF89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0F69BDF0-E94E-4400-AAE0-38ED4C2E5C9A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
   <si>
     <t>document</t>
   </si>
@@ -114,6 +114,42 @@
   </si>
   <si>
     <t>The death occurred at 33A Snowbird Gardens, Joondalup, Western Australia (page 1)</t>
+  </si>
+  <si>
+    <t>Did the coroner make recommendations for future prevention? If yes, what were they?</t>
+  </si>
+  <si>
+    <t>Yes. The coroner noted that Dr. Nathan Gibson (Chief Psychiatrist) had initiated development of a Mental Health Act orientation and training program for all consultant psychiatrists to clarify the legal requirements for detaining and treating patients with personality disorders (page 20).</t>
+  </si>
+  <si>
+    <t>Differentiate between the immediate cause of death and contributing factors.</t>
+  </si>
+  <si>
+    <t>Immediate cause: Ligature compression of the neck (hanging) (page 14). Contributing factors: Substance abuse, personality disorder, pending court case, strained relationship with his mother, and recent absconding from psychiatric care (pages 9–13, 20)</t>
+  </si>
+  <si>
+    <t>Did the coroner evaluate the adequacy of supervision, treatment, or care provided? Explain the conclusion.</t>
+  </si>
+  <si>
+    <t>Yes. The coroner concluded that Graylands Hospital staff provided reasonable and appropriate treatment and supervision. Although there were minor issues with record-keeping and a 45-minute delay in declaring him AWOL, these were not contributory to the death. Staff acted under the “least restrictive” principle of care (pages 15–17).</t>
+  </si>
+  <si>
+    <t>Forkin-finding-2015</t>
+  </si>
+  <si>
+    <t>Forkin-finding-2016</t>
+  </si>
+  <si>
+    <t>Forkin-finding-2017</t>
+  </si>
+  <si>
+    <t>Forkin-finding-2018</t>
+  </si>
+  <si>
+    <t>Does this case highlight any broader patterns or lessons relevant to public safety or institutional care?</t>
+  </si>
+  <si>
+    <t>Yes. The case highlights the complex challenges in managing patients with personality and substance-use disorders and the need for clearer guidance under the Mental Health Act. It also emphasized system improvements in record-keeping, risk assessment, and staff training, which were implemented after the inquest (pages 18–20)</t>
   </si>
 </sst>
 </file>
@@ -136,13 +172,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF242424"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -168,11 +205,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -508,27 +552,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B5BAC7C-5A53-42B5-9FED-64D1BF51DBEF}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.1796875" customWidth="1"/>
-    <col min="2" max="2" width="75.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="75.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.1796875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="103.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="255.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -539,10 +584,10 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -550,109 +595,150 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="A5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="A8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="A12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>23</v>
       </c>
     </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="C14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>